--- a/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/DuomenysTestui/visi_zive_irasai_atrankai._modif_v1 - Darb - testui_updated_added_ml_noise.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/DuomenysTestui/visi_zive_irasai_atrankai._modif_v1 - Darb - testui_updated_added_ml_noise.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="1900" windowWidth="19200" windowHeight="7710" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="380" yWindow="380" windowWidth="18600" windowHeight="9420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -41,7 +41,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,11 @@
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -120,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -156,6 +161,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.6328125" customWidth="1" style="13" min="3" max="3"/>
@@ -1170,39 +1178,41 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>1001_3</t>
+          <t>1001_4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>127999</v>
+        <v>115199</v>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>1626933.71</t>
+          <t>1626934.963</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2222</v>
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>xx</t>
         </is>
       </c>
       <c r="I7" s="8" t="n">
-        <v>869</v>
+        <v>763</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>865</v>
+        <v>761</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7" s="15" t="n">
         <v>0</v>
@@ -1211,22 +1221,22 @@
         <v>0</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="15" t="n">
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>3339</v>
+        <v>3762</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="T7" s="8" t="n">
         <v>0</v>
@@ -1239,12 +1249,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>FULLY_ANNOTATED_PROFESSIONALLY; FOR_EXTERNAL_ANNOTATING</t>
+          <t>PSEUDO_ANNOTATED</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>60f9188487cf6678b43780c3</t>
+          <t>60f9188487cf6632713780c5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1252,75 +1262,73 @@
           <t>60a917b354352a3df86dc1f2</t>
         </is>
       </c>
-      <c r="Z7" s="5" t="inlineStr">
-        <is>
-          <t>BW nedidelis, bet nuolatinis, yra ryškių EMG epizodų. Kokybė nebloga, žymėjimas koreguotas, tačiau nors triukšmai pažymėti, bet vis tiek dar išlenda silpni raumenų triukšmai, mokymui nerekomenduojamas</t>
+      <c r="Z7" s="6" t="inlineStr">
+        <is>
+          <t>Paskutinės 16 sekundžių diržas nuimtas</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>1001_4</t>
+          <t>1001_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>115199</v>
+        <v>127999</v>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>1626934.963</t>
+          <t>1626931.201</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2222</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>806</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>805</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>xx</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>763</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>761</v>
-      </c>
-      <c r="K8" s="16" t="n">
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2594</v>
+      </c>
+      <c r="S8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3762</v>
-      </c>
-      <c r="S8" s="9" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T8" s="8" t="n">
         <v>0</v>
       </c>
@@ -1332,12 +1340,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>PSEUDO_ANNOTATED</t>
+          <t>FULLY_ANNOTATED_PROFESSIONALLY; FOR_EXTERNAL_ANNOTATING</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>60f9188487cf6632713780c5</t>
+          <t>60f9188487cf66240e3780bf</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1345,72 +1353,77 @@
           <t>60a917b354352a3df86dc1f2</t>
         </is>
       </c>
-      <c r="Z8" s="6" t="inlineStr">
-        <is>
-          <t>Paskutinės 16 sekundžių diržas nuimtas</t>
+      <c r="Z8" s="5" t="inlineStr">
+        <is>
+          <t>Neaišku, kas yra ties 12300 klausimas gydytojui. Gal verta užblokuoti 3 pūpsnius pradedant reikšme 68100, gal dar 2 - ties 92700, nors dabartiniam ML nepakenkė. Kokybė nebloga, žymėjimas koreguotas , tačiau nors triukšmai pažymėti, bet vis tiek dar išlenda silpni raumenų triukšmai, mokymui nerekomenduojamas</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>1001_5</t>
+          <t>1001_6</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>127999</v>
+        <v>128000</v>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>1626931.201</t>
+          <t>1670188.752</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>2222</v>
+        <v>1111</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>J,N</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="I9" s="8" t="n">
-        <v>806</v>
+        <v>720</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>805</v>
+        <v>718</v>
       </c>
       <c r="K9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="16" t="n">
+      <c r="O9" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="O9" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>2594</v>
+        <v>300</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="T9" s="8" t="n">
         <v>0</v>
@@ -1423,29 +1436,24 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>FULLY_ANNOTATED_PROFESSIONALLY; FOR_EXTERNAL_ANNOTATING</t>
+          <t>FULLY_ANNOTATED_PROFESSIONALLY; NOISES_ANNOTATED; AI_DATASET</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>60f9188487cf66240e3780bf</t>
+          <t>638d8f609e4d4309eebbb0f1</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>60a917b354352a3df86dc1f2</t>
-        </is>
-      </c>
-      <c r="Z9" s="5" t="inlineStr">
-        <is>
-          <t>Neaišku, kas yra ties 12300 klausimas gydytojui. Gal verta užblokuoti 3 pūpsnius pradedant reikšme 68100, gal dar 2 - ties 92700, nors dabartiniam ML nepakenkė. Kokybė nebloga, žymėjimas koreguotas , tačiau nors triukšmai pažymėti, bet vis tiek dar išlenda silpni raumenų triukšmai, mokymui nerekomenduojamas</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>1001_6</t>
+          <t>1001_7</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1453,60 +1461,55 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>1670188.752</t>
+          <t>1670177.65</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1111</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>J,N</t>
-        </is>
+        <v>2222</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I10" s="8" t="n">
-        <v>720</v>
+        <v>801</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>718</v>
+        <v>798</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="T10" s="8" t="n">
         <v>0</v>
@@ -1519,24 +1522,29 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>FULLY_ANNOTATED_PROFESSIONALLY; NOISES_ANNOTATED; AI_DATASET</t>
+          <t>FULLY_ANNOTATED_PROFESSIONALLY; FOR_EXTERNAL_ANNOTATING</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>638d8f609e4d4309eebbb0f1</t>
+          <t>638d8e519e4d43245abbb0c5</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>60a917b354352a3df86dc1f2</t>
+        </is>
+      </c>
+      <c r="Z10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Švarumo lygis didžojoje dalyje arti 10, tačiau apie vidurį yra ilgas fragmentas su nežymėtu silpnu# raumenų triukšmu. Žymėjimas koreguotas, dėl įtraukimo į mokymo grupę, abejotina </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>1001_7</t>
+          <t>1001_8</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1544,55 +1552,60 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>1670177.65</t>
+          <t>1670183.201</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1111</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>J,N</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>739</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>737</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2222</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>801</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>798</v>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T11" s="8" t="n">
         <v>0</v>
@@ -1605,70 +1618,62 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>FULLY_ANNOTATED_PROFESSIONALLY; FOR_EXTERNAL_ANNOTATING</t>
+          <t>FULLY_ANNOTATED_PROFESSIONALLY; NOISES_ANNOTATED; AI_DATASET</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>638d8e519e4d43245abbb0c5</t>
+          <t>638d8f5d9e4d43301ebbb0df</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
           <t>60a917b354352a3df86dc1f2</t>
-        </is>
-      </c>
-      <c r="Z11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Švarumo lygis didžojoje dalyje arti 10, tačiau apie vidurį yra ilgas fragmentas su nežymėtu silpnu# raumenų triukšmu. Žymėjimas koreguotas, dėl įtraukimo į mokymo grupę, abejotina </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>1001_8</t>
+          <t>1003_0</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>128000</v>
+        <v>127999</v>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>1670183.201</t>
+          <t>1630726.223</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>604</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>603</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1111</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>J,N</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>739</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>737</v>
-      </c>
-      <c r="K12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="15" t="n">
-        <v>2</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1676,19 +1681,19 @@
         <v>0</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T12" s="8" t="n">
         <v>0</v>
@@ -1701,82 +1706,65 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>FULLY_ANNOTATED_PROFESSIONALLY; NOISES_ANNOTATED; AI_DATASET</t>
+          <t>FULLY_ANNOTATED_PROFESSIONALLY</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>638d8f5d9e4d43301ebbb0df</t>
+          <t>613f57ea3d08d45609cdcc86</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>60a917b354352a3df86dc1f2</t>
+          <t>613b1bc63d08d41309cdc8f1</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>1003_0</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="n"/>
       <c r="B13" t="n">
         <v>127999</v>
       </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>1630726.223</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>1626933.71</t>
+        </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>604</v>
+        <v>869</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>603</v>
+        <v>865</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="16" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3339</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T13" s="8" t="n">
         <v>0</v>
@@ -1789,19 +1777,97 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>FULLY_ANNOTATED_PROFESSIONALLY</t>
+          <t>FULLY_ANNOTATED_PROFESSIONALLY; FOR_EXTERNAL_ANNOTATING</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>613f57ea3d08d45609cdcc86</t>
+          <t>60f9188487cf6678b43780c3</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>613b1bc63d08d41309cdc8f1</t>
-        </is>
-      </c>
+          <t>60a917b354352a3df86dc1f2</t>
+        </is>
+      </c>
+      <c r="Z13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" t="n">
+        <v>128000</v>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>1740295.071</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ž,N</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>671</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>662</v>
+      </c>
+      <c r="K14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>11</v>
+      </c>
+      <c r="R14" t="n">
+        <v>9711</v>
+      </c>
+      <c r="S14" s="9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>FULLY_ANNOTATED_PROFESSIONALLY; NOISES_ANNOTATED; AI_DATASET</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>67bad7b24cf53e79dfed20fb</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>607efbd094e6ea3b5a1ab959</t>
+        </is>
+      </c>
+      <c r="Z14" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
